--- a/WB4_jar一覧.xlsx
+++ b/WB4_jar一覧.xlsx
@@ -5,18 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\90.個人フォルダ\DIR-IS德永\調査依頼\xxxx_PBxxxxxxxx_ライブラリ一覧作成_調査依頼\調査依頼\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\sys.dir.co.jp\document\共通エリア\金融システム\WB4\WB3_1\00.共通認識フォルダ\00.管理\99.その他\脆弱性調査\xxxx_PBxxxxxxxx_ライブラリ一覧作成_調査依頼\調査依頼\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BFA8EF-2A87-4E39-8A3E-075E7406EA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789420CF-6A6B-4CA5-ADFB-AD51120C5299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AP_jar一覧" sheetId="2" r:id="rId1"/>
+    <sheet name="PR_jar一覧" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AP_jar一覧!$A$2:$F$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">PR_jar一覧!$A$4:$G$102</definedName>
     <definedName name="Env_all">#REF!</definedName>
     <definedName name="Institutions">#REF!</definedName>
   </definedNames>
@@ -55,8 +57,34 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>山口 和紀/DIR金融システム部</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{2020EB13-4928-4503-ACA4-A044FC743684}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">DIR内製か否か
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="257">
   <si>
     <t>記載済みのため調査割愛</t>
     <rPh sb="0" eb="3">
@@ -840,6 +868,134 @@
     <t>脆弱性なしのバージョン</t>
     <rPh sb="0" eb="3">
       <t>ゼイジャクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ICCとSVNで差分があった。→SVNにないファイルをICCが保持していたため、ICCから一覧を作成</t>
+    <rPh sb="8" eb="10">
+      <t>サブン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ホジ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>また、APと同じjarについてはAPで調査済みのため調査を割愛する</t>
+    <rPh sb="6" eb="7">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>チョウサズ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カツアイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>http://w3ttsvn10/svn/webbroker3_pr/Applications/trunk/webbroker3/WEB-INF/lib</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>APで調査済みのため調査割愛</t>
+    <rPh sb="3" eb="6">
+      <t>チョウサズ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カツアイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>cgiservlet-1.0.0.jar</t>
+  </si>
+  <si>
+    <t>commons-fileupload-1.4.jar</t>
+  </si>
+  <si>
+    <t>Apache Commons FileUpload</t>
+  </si>
+  <si>
+    <t>commons-io-2.6.jar</t>
+  </si>
+  <si>
+    <t>Apache Commons IO</t>
+  </si>
+  <si>
+    <t>concurrent.jar</t>
+  </si>
+  <si>
+    <t>1.3.4</t>
+  </si>
+  <si>
+    <t>http://gee.cs.oswego.edu/dl/classes/EDU/oswego/cs/dl/util/concurrent/intro.html</t>
+  </si>
+  <si>
+    <t>util.concurrent</t>
+  </si>
+  <si>
+    <t>csv.jar</t>
+  </si>
+  <si>
+    <t>gft_connection.jar</t>
+  </si>
+  <si>
+    <t>jmxtools.jar</t>
+  </si>
+  <si>
+    <t>jsonic-1.3.0.jar</t>
+  </si>
+  <si>
+    <t>pjl-comp-filter-1.7.jar</t>
+  </si>
+  <si>
+    <t>struts.jar</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>Struts Framework</t>
+  </si>
+  <si>
+    <t>tfx_connection.jar</t>
+  </si>
+  <si>
+    <t>web3base.jar</t>
+  </si>
+  <si>
+    <t>wolf2.jar</t>
+  </si>
+  <si>
+    <t>wolf2_taglib.jar</t>
+  </si>
+  <si>
+    <t>WEB3_taglib_1.0.0</t>
+  </si>
+  <si>
+    <t>DIR-BI</t>
+  </si>
+  <si>
+    <t>WOLF2 Taglib for WebBroker3 Java 8</t>
+  </si>
+  <si>
+    <t>使用しているバージョン</t>
+    <rPh sb="0" eb="2">
+      <t>シヨウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -934,7 +1090,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -947,6 +1103,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1881,7 +2043,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="37.5">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>224</v>
       </c>
@@ -4683,4 +4845,1714 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A2B8FD-8B3C-4977-A3CD-2E94EE25AF9D}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I102"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="6.75" style="5" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="26" style="5" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="26.375" style="5" customWidth="1"/>
+    <col min="10" max="253" width="9" style="5"/>
+    <col min="254" max="254" width="6.75" style="5" customWidth="1"/>
+    <col min="255" max="255" width="18.125" style="5" customWidth="1"/>
+    <col min="256" max="256" width="14.75" style="5" customWidth="1"/>
+    <col min="257" max="257" width="15.625" style="5" customWidth="1"/>
+    <col min="258" max="260" width="9" style="5"/>
+    <col min="261" max="261" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="262" max="262" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="263" max="509" width="9" style="5"/>
+    <col min="510" max="510" width="6.75" style="5" customWidth="1"/>
+    <col min="511" max="511" width="18.125" style="5" customWidth="1"/>
+    <col min="512" max="512" width="14.75" style="5" customWidth="1"/>
+    <col min="513" max="513" width="15.625" style="5" customWidth="1"/>
+    <col min="514" max="516" width="9" style="5"/>
+    <col min="517" max="517" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="519" max="765" width="9" style="5"/>
+    <col min="766" max="766" width="6.75" style="5" customWidth="1"/>
+    <col min="767" max="767" width="18.125" style="5" customWidth="1"/>
+    <col min="768" max="768" width="14.75" style="5" customWidth="1"/>
+    <col min="769" max="769" width="15.625" style="5" customWidth="1"/>
+    <col min="770" max="772" width="9" style="5"/>
+    <col min="773" max="773" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="774" max="774" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="775" max="1021" width="9" style="5"/>
+    <col min="1022" max="1022" width="6.75" style="5" customWidth="1"/>
+    <col min="1023" max="1023" width="18.125" style="5" customWidth="1"/>
+    <col min="1024" max="1024" width="14.75" style="5" customWidth="1"/>
+    <col min="1025" max="1025" width="15.625" style="5" customWidth="1"/>
+    <col min="1026" max="1028" width="9" style="5"/>
+    <col min="1029" max="1029" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1030" max="1030" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="1031" max="1277" width="9" style="5"/>
+    <col min="1278" max="1278" width="6.75" style="5" customWidth="1"/>
+    <col min="1279" max="1279" width="18.125" style="5" customWidth="1"/>
+    <col min="1280" max="1280" width="14.75" style="5" customWidth="1"/>
+    <col min="1281" max="1281" width="15.625" style="5" customWidth="1"/>
+    <col min="1282" max="1284" width="9" style="5"/>
+    <col min="1285" max="1285" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1286" max="1286" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="1287" max="1533" width="9" style="5"/>
+    <col min="1534" max="1534" width="6.75" style="5" customWidth="1"/>
+    <col min="1535" max="1535" width="18.125" style="5" customWidth="1"/>
+    <col min="1536" max="1536" width="14.75" style="5" customWidth="1"/>
+    <col min="1537" max="1537" width="15.625" style="5" customWidth="1"/>
+    <col min="1538" max="1540" width="9" style="5"/>
+    <col min="1541" max="1541" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1542" max="1542" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="1543" max="1789" width="9" style="5"/>
+    <col min="1790" max="1790" width="6.75" style="5" customWidth="1"/>
+    <col min="1791" max="1791" width="18.125" style="5" customWidth="1"/>
+    <col min="1792" max="1792" width="14.75" style="5" customWidth="1"/>
+    <col min="1793" max="1793" width="15.625" style="5" customWidth="1"/>
+    <col min="1794" max="1796" width="9" style="5"/>
+    <col min="1797" max="1797" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1798" max="1798" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="1799" max="2045" width="9" style="5"/>
+    <col min="2046" max="2046" width="6.75" style="5" customWidth="1"/>
+    <col min="2047" max="2047" width="18.125" style="5" customWidth="1"/>
+    <col min="2048" max="2048" width="14.75" style="5" customWidth="1"/>
+    <col min="2049" max="2049" width="15.625" style="5" customWidth="1"/>
+    <col min="2050" max="2052" width="9" style="5"/>
+    <col min="2053" max="2053" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2054" max="2054" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="2055" max="2301" width="9" style="5"/>
+    <col min="2302" max="2302" width="6.75" style="5" customWidth="1"/>
+    <col min="2303" max="2303" width="18.125" style="5" customWidth="1"/>
+    <col min="2304" max="2304" width="14.75" style="5" customWidth="1"/>
+    <col min="2305" max="2305" width="15.625" style="5" customWidth="1"/>
+    <col min="2306" max="2308" width="9" style="5"/>
+    <col min="2309" max="2309" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2310" max="2310" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="2311" max="2557" width="9" style="5"/>
+    <col min="2558" max="2558" width="6.75" style="5" customWidth="1"/>
+    <col min="2559" max="2559" width="18.125" style="5" customWidth="1"/>
+    <col min="2560" max="2560" width="14.75" style="5" customWidth="1"/>
+    <col min="2561" max="2561" width="15.625" style="5" customWidth="1"/>
+    <col min="2562" max="2564" width="9" style="5"/>
+    <col min="2565" max="2565" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2566" max="2566" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="2567" max="2813" width="9" style="5"/>
+    <col min="2814" max="2814" width="6.75" style="5" customWidth="1"/>
+    <col min="2815" max="2815" width="18.125" style="5" customWidth="1"/>
+    <col min="2816" max="2816" width="14.75" style="5" customWidth="1"/>
+    <col min="2817" max="2817" width="15.625" style="5" customWidth="1"/>
+    <col min="2818" max="2820" width="9" style="5"/>
+    <col min="2821" max="2821" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2822" max="2822" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="2823" max="3069" width="9" style="5"/>
+    <col min="3070" max="3070" width="6.75" style="5" customWidth="1"/>
+    <col min="3071" max="3071" width="18.125" style="5" customWidth="1"/>
+    <col min="3072" max="3072" width="14.75" style="5" customWidth="1"/>
+    <col min="3073" max="3073" width="15.625" style="5" customWidth="1"/>
+    <col min="3074" max="3076" width="9" style="5"/>
+    <col min="3077" max="3077" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3078" max="3078" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="3079" max="3325" width="9" style="5"/>
+    <col min="3326" max="3326" width="6.75" style="5" customWidth="1"/>
+    <col min="3327" max="3327" width="18.125" style="5" customWidth="1"/>
+    <col min="3328" max="3328" width="14.75" style="5" customWidth="1"/>
+    <col min="3329" max="3329" width="15.625" style="5" customWidth="1"/>
+    <col min="3330" max="3332" width="9" style="5"/>
+    <col min="3333" max="3333" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3334" max="3334" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="3335" max="3581" width="9" style="5"/>
+    <col min="3582" max="3582" width="6.75" style="5" customWidth="1"/>
+    <col min="3583" max="3583" width="18.125" style="5" customWidth="1"/>
+    <col min="3584" max="3584" width="14.75" style="5" customWidth="1"/>
+    <col min="3585" max="3585" width="15.625" style="5" customWidth="1"/>
+    <col min="3586" max="3588" width="9" style="5"/>
+    <col min="3589" max="3589" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3590" max="3590" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="3591" max="3837" width="9" style="5"/>
+    <col min="3838" max="3838" width="6.75" style="5" customWidth="1"/>
+    <col min="3839" max="3839" width="18.125" style="5" customWidth="1"/>
+    <col min="3840" max="3840" width="14.75" style="5" customWidth="1"/>
+    <col min="3841" max="3841" width="15.625" style="5" customWidth="1"/>
+    <col min="3842" max="3844" width="9" style="5"/>
+    <col min="3845" max="3845" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3846" max="3846" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="3847" max="4093" width="9" style="5"/>
+    <col min="4094" max="4094" width="6.75" style="5" customWidth="1"/>
+    <col min="4095" max="4095" width="18.125" style="5" customWidth="1"/>
+    <col min="4096" max="4096" width="14.75" style="5" customWidth="1"/>
+    <col min="4097" max="4097" width="15.625" style="5" customWidth="1"/>
+    <col min="4098" max="4100" width="9" style="5"/>
+    <col min="4101" max="4101" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4102" max="4102" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4103" max="4349" width="9" style="5"/>
+    <col min="4350" max="4350" width="6.75" style="5" customWidth="1"/>
+    <col min="4351" max="4351" width="18.125" style="5" customWidth="1"/>
+    <col min="4352" max="4352" width="14.75" style="5" customWidth="1"/>
+    <col min="4353" max="4353" width="15.625" style="5" customWidth="1"/>
+    <col min="4354" max="4356" width="9" style="5"/>
+    <col min="4357" max="4357" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4358" max="4358" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4359" max="4605" width="9" style="5"/>
+    <col min="4606" max="4606" width="6.75" style="5" customWidth="1"/>
+    <col min="4607" max="4607" width="18.125" style="5" customWidth="1"/>
+    <col min="4608" max="4608" width="14.75" style="5" customWidth="1"/>
+    <col min="4609" max="4609" width="15.625" style="5" customWidth="1"/>
+    <col min="4610" max="4612" width="9" style="5"/>
+    <col min="4613" max="4613" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4614" max="4614" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4615" max="4861" width="9" style="5"/>
+    <col min="4862" max="4862" width="6.75" style="5" customWidth="1"/>
+    <col min="4863" max="4863" width="18.125" style="5" customWidth="1"/>
+    <col min="4864" max="4864" width="14.75" style="5" customWidth="1"/>
+    <col min="4865" max="4865" width="15.625" style="5" customWidth="1"/>
+    <col min="4866" max="4868" width="9" style="5"/>
+    <col min="4869" max="4869" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4870" max="4870" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4871" max="5117" width="9" style="5"/>
+    <col min="5118" max="5118" width="6.75" style="5" customWidth="1"/>
+    <col min="5119" max="5119" width="18.125" style="5" customWidth="1"/>
+    <col min="5120" max="5120" width="14.75" style="5" customWidth="1"/>
+    <col min="5121" max="5121" width="15.625" style="5" customWidth="1"/>
+    <col min="5122" max="5124" width="9" style="5"/>
+    <col min="5125" max="5125" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5126" max="5126" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="5127" max="5373" width="9" style="5"/>
+    <col min="5374" max="5374" width="6.75" style="5" customWidth="1"/>
+    <col min="5375" max="5375" width="18.125" style="5" customWidth="1"/>
+    <col min="5376" max="5376" width="14.75" style="5" customWidth="1"/>
+    <col min="5377" max="5377" width="15.625" style="5" customWidth="1"/>
+    <col min="5378" max="5380" width="9" style="5"/>
+    <col min="5381" max="5381" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5382" max="5382" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="5383" max="5629" width="9" style="5"/>
+    <col min="5630" max="5630" width="6.75" style="5" customWidth="1"/>
+    <col min="5631" max="5631" width="18.125" style="5" customWidth="1"/>
+    <col min="5632" max="5632" width="14.75" style="5" customWidth="1"/>
+    <col min="5633" max="5633" width="15.625" style="5" customWidth="1"/>
+    <col min="5634" max="5636" width="9" style="5"/>
+    <col min="5637" max="5637" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5638" max="5638" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="5639" max="5885" width="9" style="5"/>
+    <col min="5886" max="5886" width="6.75" style="5" customWidth="1"/>
+    <col min="5887" max="5887" width="18.125" style="5" customWidth="1"/>
+    <col min="5888" max="5888" width="14.75" style="5" customWidth="1"/>
+    <col min="5889" max="5889" width="15.625" style="5" customWidth="1"/>
+    <col min="5890" max="5892" width="9" style="5"/>
+    <col min="5893" max="5893" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5894" max="5894" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="5895" max="6141" width="9" style="5"/>
+    <col min="6142" max="6142" width="6.75" style="5" customWidth="1"/>
+    <col min="6143" max="6143" width="18.125" style="5" customWidth="1"/>
+    <col min="6144" max="6144" width="14.75" style="5" customWidth="1"/>
+    <col min="6145" max="6145" width="15.625" style="5" customWidth="1"/>
+    <col min="6146" max="6148" width="9" style="5"/>
+    <col min="6149" max="6149" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6150" max="6150" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="6151" max="6397" width="9" style="5"/>
+    <col min="6398" max="6398" width="6.75" style="5" customWidth="1"/>
+    <col min="6399" max="6399" width="18.125" style="5" customWidth="1"/>
+    <col min="6400" max="6400" width="14.75" style="5" customWidth="1"/>
+    <col min="6401" max="6401" width="15.625" style="5" customWidth="1"/>
+    <col min="6402" max="6404" width="9" style="5"/>
+    <col min="6405" max="6405" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6406" max="6406" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="6407" max="6653" width="9" style="5"/>
+    <col min="6654" max="6654" width="6.75" style="5" customWidth="1"/>
+    <col min="6655" max="6655" width="18.125" style="5" customWidth="1"/>
+    <col min="6656" max="6656" width="14.75" style="5" customWidth="1"/>
+    <col min="6657" max="6657" width="15.625" style="5" customWidth="1"/>
+    <col min="6658" max="6660" width="9" style="5"/>
+    <col min="6661" max="6661" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6662" max="6662" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="6663" max="6909" width="9" style="5"/>
+    <col min="6910" max="6910" width="6.75" style="5" customWidth="1"/>
+    <col min="6911" max="6911" width="18.125" style="5" customWidth="1"/>
+    <col min="6912" max="6912" width="14.75" style="5" customWidth="1"/>
+    <col min="6913" max="6913" width="15.625" style="5" customWidth="1"/>
+    <col min="6914" max="6916" width="9" style="5"/>
+    <col min="6917" max="6917" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6918" max="6918" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="6919" max="7165" width="9" style="5"/>
+    <col min="7166" max="7166" width="6.75" style="5" customWidth="1"/>
+    <col min="7167" max="7167" width="18.125" style="5" customWidth="1"/>
+    <col min="7168" max="7168" width="14.75" style="5" customWidth="1"/>
+    <col min="7169" max="7169" width="15.625" style="5" customWidth="1"/>
+    <col min="7170" max="7172" width="9" style="5"/>
+    <col min="7173" max="7173" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7174" max="7174" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="7175" max="7421" width="9" style="5"/>
+    <col min="7422" max="7422" width="6.75" style="5" customWidth="1"/>
+    <col min="7423" max="7423" width="18.125" style="5" customWidth="1"/>
+    <col min="7424" max="7424" width="14.75" style="5" customWidth="1"/>
+    <col min="7425" max="7425" width="15.625" style="5" customWidth="1"/>
+    <col min="7426" max="7428" width="9" style="5"/>
+    <col min="7429" max="7429" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7430" max="7430" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="7431" max="7677" width="9" style="5"/>
+    <col min="7678" max="7678" width="6.75" style="5" customWidth="1"/>
+    <col min="7679" max="7679" width="18.125" style="5" customWidth="1"/>
+    <col min="7680" max="7680" width="14.75" style="5" customWidth="1"/>
+    <col min="7681" max="7681" width="15.625" style="5" customWidth="1"/>
+    <col min="7682" max="7684" width="9" style="5"/>
+    <col min="7685" max="7685" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7686" max="7686" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="7687" max="7933" width="9" style="5"/>
+    <col min="7934" max="7934" width="6.75" style="5" customWidth="1"/>
+    <col min="7935" max="7935" width="18.125" style="5" customWidth="1"/>
+    <col min="7936" max="7936" width="14.75" style="5" customWidth="1"/>
+    <col min="7937" max="7937" width="15.625" style="5" customWidth="1"/>
+    <col min="7938" max="7940" width="9" style="5"/>
+    <col min="7941" max="7941" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7942" max="7942" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="7943" max="8189" width="9" style="5"/>
+    <col min="8190" max="8190" width="6.75" style="5" customWidth="1"/>
+    <col min="8191" max="8191" width="18.125" style="5" customWidth="1"/>
+    <col min="8192" max="8192" width="14.75" style="5" customWidth="1"/>
+    <col min="8193" max="8193" width="15.625" style="5" customWidth="1"/>
+    <col min="8194" max="8196" width="9" style="5"/>
+    <col min="8197" max="8197" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8198" max="8198" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="8199" max="8445" width="9" style="5"/>
+    <col min="8446" max="8446" width="6.75" style="5" customWidth="1"/>
+    <col min="8447" max="8447" width="18.125" style="5" customWidth="1"/>
+    <col min="8448" max="8448" width="14.75" style="5" customWidth="1"/>
+    <col min="8449" max="8449" width="15.625" style="5" customWidth="1"/>
+    <col min="8450" max="8452" width="9" style="5"/>
+    <col min="8453" max="8453" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8454" max="8454" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="8455" max="8701" width="9" style="5"/>
+    <col min="8702" max="8702" width="6.75" style="5" customWidth="1"/>
+    <col min="8703" max="8703" width="18.125" style="5" customWidth="1"/>
+    <col min="8704" max="8704" width="14.75" style="5" customWidth="1"/>
+    <col min="8705" max="8705" width="15.625" style="5" customWidth="1"/>
+    <col min="8706" max="8708" width="9" style="5"/>
+    <col min="8709" max="8709" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8710" max="8710" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="8711" max="8957" width="9" style="5"/>
+    <col min="8958" max="8958" width="6.75" style="5" customWidth="1"/>
+    <col min="8959" max="8959" width="18.125" style="5" customWidth="1"/>
+    <col min="8960" max="8960" width="14.75" style="5" customWidth="1"/>
+    <col min="8961" max="8961" width="15.625" style="5" customWidth="1"/>
+    <col min="8962" max="8964" width="9" style="5"/>
+    <col min="8965" max="8965" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8966" max="8966" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="8967" max="9213" width="9" style="5"/>
+    <col min="9214" max="9214" width="6.75" style="5" customWidth="1"/>
+    <col min="9215" max="9215" width="18.125" style="5" customWidth="1"/>
+    <col min="9216" max="9216" width="14.75" style="5" customWidth="1"/>
+    <col min="9217" max="9217" width="15.625" style="5" customWidth="1"/>
+    <col min="9218" max="9220" width="9" style="5"/>
+    <col min="9221" max="9221" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9222" max="9222" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="9223" max="9469" width="9" style="5"/>
+    <col min="9470" max="9470" width="6.75" style="5" customWidth="1"/>
+    <col min="9471" max="9471" width="18.125" style="5" customWidth="1"/>
+    <col min="9472" max="9472" width="14.75" style="5" customWidth="1"/>
+    <col min="9473" max="9473" width="15.625" style="5" customWidth="1"/>
+    <col min="9474" max="9476" width="9" style="5"/>
+    <col min="9477" max="9477" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9478" max="9478" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="9479" max="9725" width="9" style="5"/>
+    <col min="9726" max="9726" width="6.75" style="5" customWidth="1"/>
+    <col min="9727" max="9727" width="18.125" style="5" customWidth="1"/>
+    <col min="9728" max="9728" width="14.75" style="5" customWidth="1"/>
+    <col min="9729" max="9729" width="15.625" style="5" customWidth="1"/>
+    <col min="9730" max="9732" width="9" style="5"/>
+    <col min="9733" max="9733" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9734" max="9734" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="9735" max="9981" width="9" style="5"/>
+    <col min="9982" max="9982" width="6.75" style="5" customWidth="1"/>
+    <col min="9983" max="9983" width="18.125" style="5" customWidth="1"/>
+    <col min="9984" max="9984" width="14.75" style="5" customWidth="1"/>
+    <col min="9985" max="9985" width="15.625" style="5" customWidth="1"/>
+    <col min="9986" max="9988" width="9" style="5"/>
+    <col min="9989" max="9989" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9990" max="9990" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="9991" max="10237" width="9" style="5"/>
+    <col min="10238" max="10238" width="6.75" style="5" customWidth="1"/>
+    <col min="10239" max="10239" width="18.125" style="5" customWidth="1"/>
+    <col min="10240" max="10240" width="14.75" style="5" customWidth="1"/>
+    <col min="10241" max="10241" width="15.625" style="5" customWidth="1"/>
+    <col min="10242" max="10244" width="9" style="5"/>
+    <col min="10245" max="10245" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10246" max="10246" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="10247" max="10493" width="9" style="5"/>
+    <col min="10494" max="10494" width="6.75" style="5" customWidth="1"/>
+    <col min="10495" max="10495" width="18.125" style="5" customWidth="1"/>
+    <col min="10496" max="10496" width="14.75" style="5" customWidth="1"/>
+    <col min="10497" max="10497" width="15.625" style="5" customWidth="1"/>
+    <col min="10498" max="10500" width="9" style="5"/>
+    <col min="10501" max="10501" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10502" max="10502" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="10503" max="10749" width="9" style="5"/>
+    <col min="10750" max="10750" width="6.75" style="5" customWidth="1"/>
+    <col min="10751" max="10751" width="18.125" style="5" customWidth="1"/>
+    <col min="10752" max="10752" width="14.75" style="5" customWidth="1"/>
+    <col min="10753" max="10753" width="15.625" style="5" customWidth="1"/>
+    <col min="10754" max="10756" width="9" style="5"/>
+    <col min="10757" max="10757" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10758" max="10758" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="10759" max="11005" width="9" style="5"/>
+    <col min="11006" max="11006" width="6.75" style="5" customWidth="1"/>
+    <col min="11007" max="11007" width="18.125" style="5" customWidth="1"/>
+    <col min="11008" max="11008" width="14.75" style="5" customWidth="1"/>
+    <col min="11009" max="11009" width="15.625" style="5" customWidth="1"/>
+    <col min="11010" max="11012" width="9" style="5"/>
+    <col min="11013" max="11013" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11014" max="11014" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="11015" max="11261" width="9" style="5"/>
+    <col min="11262" max="11262" width="6.75" style="5" customWidth="1"/>
+    <col min="11263" max="11263" width="18.125" style="5" customWidth="1"/>
+    <col min="11264" max="11264" width="14.75" style="5" customWidth="1"/>
+    <col min="11265" max="11265" width="15.625" style="5" customWidth="1"/>
+    <col min="11266" max="11268" width="9" style="5"/>
+    <col min="11269" max="11269" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11270" max="11270" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="11271" max="11517" width="9" style="5"/>
+    <col min="11518" max="11518" width="6.75" style="5" customWidth="1"/>
+    <col min="11519" max="11519" width="18.125" style="5" customWidth="1"/>
+    <col min="11520" max="11520" width="14.75" style="5" customWidth="1"/>
+    <col min="11521" max="11521" width="15.625" style="5" customWidth="1"/>
+    <col min="11522" max="11524" width="9" style="5"/>
+    <col min="11525" max="11525" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11526" max="11526" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="11527" max="11773" width="9" style="5"/>
+    <col min="11774" max="11774" width="6.75" style="5" customWidth="1"/>
+    <col min="11775" max="11775" width="18.125" style="5" customWidth="1"/>
+    <col min="11776" max="11776" width="14.75" style="5" customWidth="1"/>
+    <col min="11777" max="11777" width="15.625" style="5" customWidth="1"/>
+    <col min="11778" max="11780" width="9" style="5"/>
+    <col min="11781" max="11781" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11782" max="11782" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="11783" max="12029" width="9" style="5"/>
+    <col min="12030" max="12030" width="6.75" style="5" customWidth="1"/>
+    <col min="12031" max="12031" width="18.125" style="5" customWidth="1"/>
+    <col min="12032" max="12032" width="14.75" style="5" customWidth="1"/>
+    <col min="12033" max="12033" width="15.625" style="5" customWidth="1"/>
+    <col min="12034" max="12036" width="9" style="5"/>
+    <col min="12037" max="12037" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12038" max="12038" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="12039" max="12285" width="9" style="5"/>
+    <col min="12286" max="12286" width="6.75" style="5" customWidth="1"/>
+    <col min="12287" max="12287" width="18.125" style="5" customWidth="1"/>
+    <col min="12288" max="12288" width="14.75" style="5" customWidth="1"/>
+    <col min="12289" max="12289" width="15.625" style="5" customWidth="1"/>
+    <col min="12290" max="12292" width="9" style="5"/>
+    <col min="12293" max="12293" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12294" max="12294" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="12295" max="12541" width="9" style="5"/>
+    <col min="12542" max="12542" width="6.75" style="5" customWidth="1"/>
+    <col min="12543" max="12543" width="18.125" style="5" customWidth="1"/>
+    <col min="12544" max="12544" width="14.75" style="5" customWidth="1"/>
+    <col min="12545" max="12545" width="15.625" style="5" customWidth="1"/>
+    <col min="12546" max="12548" width="9" style="5"/>
+    <col min="12549" max="12549" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12550" max="12550" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="12551" max="12797" width="9" style="5"/>
+    <col min="12798" max="12798" width="6.75" style="5" customWidth="1"/>
+    <col min="12799" max="12799" width="18.125" style="5" customWidth="1"/>
+    <col min="12800" max="12800" width="14.75" style="5" customWidth="1"/>
+    <col min="12801" max="12801" width="15.625" style="5" customWidth="1"/>
+    <col min="12802" max="12804" width="9" style="5"/>
+    <col min="12805" max="12805" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12806" max="12806" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="12807" max="13053" width="9" style="5"/>
+    <col min="13054" max="13054" width="6.75" style="5" customWidth="1"/>
+    <col min="13055" max="13055" width="18.125" style="5" customWidth="1"/>
+    <col min="13056" max="13056" width="14.75" style="5" customWidth="1"/>
+    <col min="13057" max="13057" width="15.625" style="5" customWidth="1"/>
+    <col min="13058" max="13060" width="9" style="5"/>
+    <col min="13061" max="13061" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13062" max="13062" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="13063" max="13309" width="9" style="5"/>
+    <col min="13310" max="13310" width="6.75" style="5" customWidth="1"/>
+    <col min="13311" max="13311" width="18.125" style="5" customWidth="1"/>
+    <col min="13312" max="13312" width="14.75" style="5" customWidth="1"/>
+    <col min="13313" max="13313" width="15.625" style="5" customWidth="1"/>
+    <col min="13314" max="13316" width="9" style="5"/>
+    <col min="13317" max="13317" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13318" max="13318" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="13319" max="13565" width="9" style="5"/>
+    <col min="13566" max="13566" width="6.75" style="5" customWidth="1"/>
+    <col min="13567" max="13567" width="18.125" style="5" customWidth="1"/>
+    <col min="13568" max="13568" width="14.75" style="5" customWidth="1"/>
+    <col min="13569" max="13569" width="15.625" style="5" customWidth="1"/>
+    <col min="13570" max="13572" width="9" style="5"/>
+    <col min="13573" max="13573" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13574" max="13574" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="13575" max="13821" width="9" style="5"/>
+    <col min="13822" max="13822" width="6.75" style="5" customWidth="1"/>
+    <col min="13823" max="13823" width="18.125" style="5" customWidth="1"/>
+    <col min="13824" max="13824" width="14.75" style="5" customWidth="1"/>
+    <col min="13825" max="13825" width="15.625" style="5" customWidth="1"/>
+    <col min="13826" max="13828" width="9" style="5"/>
+    <col min="13829" max="13829" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13830" max="13830" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="13831" max="14077" width="9" style="5"/>
+    <col min="14078" max="14078" width="6.75" style="5" customWidth="1"/>
+    <col min="14079" max="14079" width="18.125" style="5" customWidth="1"/>
+    <col min="14080" max="14080" width="14.75" style="5" customWidth="1"/>
+    <col min="14081" max="14081" width="15.625" style="5" customWidth="1"/>
+    <col min="14082" max="14084" width="9" style="5"/>
+    <col min="14085" max="14085" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14086" max="14086" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="14087" max="14333" width="9" style="5"/>
+    <col min="14334" max="14334" width="6.75" style="5" customWidth="1"/>
+    <col min="14335" max="14335" width="18.125" style="5" customWidth="1"/>
+    <col min="14336" max="14336" width="14.75" style="5" customWidth="1"/>
+    <col min="14337" max="14337" width="15.625" style="5" customWidth="1"/>
+    <col min="14338" max="14340" width="9" style="5"/>
+    <col min="14341" max="14341" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14342" max="14342" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="14343" max="14589" width="9" style="5"/>
+    <col min="14590" max="14590" width="6.75" style="5" customWidth="1"/>
+    <col min="14591" max="14591" width="18.125" style="5" customWidth="1"/>
+    <col min="14592" max="14592" width="14.75" style="5" customWidth="1"/>
+    <col min="14593" max="14593" width="15.625" style="5" customWidth="1"/>
+    <col min="14594" max="14596" width="9" style="5"/>
+    <col min="14597" max="14597" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14598" max="14598" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="14599" max="14845" width="9" style="5"/>
+    <col min="14846" max="14846" width="6.75" style="5" customWidth="1"/>
+    <col min="14847" max="14847" width="18.125" style="5" customWidth="1"/>
+    <col min="14848" max="14848" width="14.75" style="5" customWidth="1"/>
+    <col min="14849" max="14849" width="15.625" style="5" customWidth="1"/>
+    <col min="14850" max="14852" width="9" style="5"/>
+    <col min="14853" max="14853" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14854" max="14854" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="14855" max="15101" width="9" style="5"/>
+    <col min="15102" max="15102" width="6.75" style="5" customWidth="1"/>
+    <col min="15103" max="15103" width="18.125" style="5" customWidth="1"/>
+    <col min="15104" max="15104" width="14.75" style="5" customWidth="1"/>
+    <col min="15105" max="15105" width="15.625" style="5" customWidth="1"/>
+    <col min="15106" max="15108" width="9" style="5"/>
+    <col min="15109" max="15109" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15110" max="15110" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="15111" max="15357" width="9" style="5"/>
+    <col min="15358" max="15358" width="6.75" style="5" customWidth="1"/>
+    <col min="15359" max="15359" width="18.125" style="5" customWidth="1"/>
+    <col min="15360" max="15360" width="14.75" style="5" customWidth="1"/>
+    <col min="15361" max="15361" width="15.625" style="5" customWidth="1"/>
+    <col min="15362" max="15364" width="9" style="5"/>
+    <col min="15365" max="15365" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15366" max="15366" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="15367" max="15613" width="9" style="5"/>
+    <col min="15614" max="15614" width="6.75" style="5" customWidth="1"/>
+    <col min="15615" max="15615" width="18.125" style="5" customWidth="1"/>
+    <col min="15616" max="15616" width="14.75" style="5" customWidth="1"/>
+    <col min="15617" max="15617" width="15.625" style="5" customWidth="1"/>
+    <col min="15618" max="15620" width="9" style="5"/>
+    <col min="15621" max="15621" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15622" max="15622" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="15623" max="15869" width="9" style="5"/>
+    <col min="15870" max="15870" width="6.75" style="5" customWidth="1"/>
+    <col min="15871" max="15871" width="18.125" style="5" customWidth="1"/>
+    <col min="15872" max="15872" width="14.75" style="5" customWidth="1"/>
+    <col min="15873" max="15873" width="15.625" style="5" customWidth="1"/>
+    <col min="15874" max="15876" width="9" style="5"/>
+    <col min="15877" max="15877" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15878" max="15878" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="15879" max="16125" width="9" style="5"/>
+    <col min="16126" max="16126" width="6.75" style="5" customWidth="1"/>
+    <col min="16127" max="16127" width="18.125" style="5" customWidth="1"/>
+    <col min="16128" max="16128" width="14.75" style="5" customWidth="1"/>
+    <col min="16129" max="16129" width="15.625" style="5" customWidth="1"/>
+    <col min="16130" max="16132" width="9" style="5"/>
+    <col min="16133" max="16133" width="32.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="16134" max="16134" width="28.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="16135" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="112.5" hidden="1">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" hidden="1">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1">
+      <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1">
+      <c r="A18" s="5">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1">
+      <c r="A19" s="5">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1">
+      <c r="A20" s="5">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1">
+      <c r="A21" s="5">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1">
+      <c r="A22" s="5">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1">
+      <c r="A23" s="5">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1">
+      <c r="A24" s="5">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1">
+      <c r="A25" s="5">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1">
+      <c r="A26" s="5">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1">
+      <c r="A27" s="5">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" hidden="1">
+      <c r="A28" s="5">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1">
+      <c r="A29" s="5">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1">
+      <c r="A30" s="5">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" hidden="1">
+      <c r="A31" s="5">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1">
+      <c r="A32" s="5">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" hidden="1">
+      <c r="A33" s="5">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1">
+      <c r="A34" s="5">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1">
+      <c r="A35" s="5">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1">
+      <c r="A36" s="5">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1">
+      <c r="A37" s="5">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1">
+      <c r="A38" s="5">
+        <v>34</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1">
+      <c r="A39" s="5">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1">
+      <c r="A40" s="5">
+        <v>36</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1">
+      <c r="A41" s="5">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1">
+      <c r="A42" s="5">
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" hidden="1">
+      <c r="A43" s="5">
+        <v>39</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1">
+      <c r="A44" s="5">
+        <v>40</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1">
+      <c r="A45" s="5">
+        <v>41</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" hidden="1">
+      <c r="A46" s="5">
+        <v>42</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1">
+      <c r="A47" s="5">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" hidden="1">
+      <c r="A48" s="5">
+        <v>44</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1">
+      <c r="A49" s="5">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1">
+      <c r="A50" s="5">
+        <v>46</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1">
+      <c r="A51" s="5">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1">
+      <c r="A52" s="5">
+        <v>48</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" hidden="1">
+      <c r="A53" s="5">
+        <v>49</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1">
+      <c r="A54" s="5">
+        <v>50</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1">
+      <c r="A55" s="5">
+        <v>51</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" hidden="1">
+      <c r="A56" s="5">
+        <v>52</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1">
+      <c r="A57" s="5">
+        <v>53</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" hidden="1">
+      <c r="A58" s="5">
+        <v>54</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" hidden="1">
+      <c r="A59" s="5">
+        <v>55</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" hidden="1">
+      <c r="A60" s="5">
+        <v>56</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" hidden="1">
+      <c r="A61" s="5">
+        <v>57</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1">
+      <c r="A62" s="5">
+        <v>58</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" hidden="1">
+      <c r="A63" s="5">
+        <v>59</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1">
+      <c r="A64" s="5">
+        <v>60</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" hidden="1">
+      <c r="A65" s="5">
+        <v>61</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" hidden="1">
+      <c r="A66" s="5">
+        <v>62</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" hidden="1">
+      <c r="A67" s="5">
+        <v>63</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" hidden="1">
+      <c r="A68" s="5">
+        <v>64</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1">
+      <c r="A69" s="5">
+        <v>65</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" hidden="1">
+      <c r="A70" s="5">
+        <v>66</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" hidden="1">
+      <c r="A71" s="5">
+        <v>67</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1">
+      <c r="A72" s="5">
+        <v>68</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" hidden="1">
+      <c r="A73" s="5">
+        <v>69</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1">
+      <c r="A74" s="5">
+        <v>70</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" hidden="1">
+      <c r="A75" s="5">
+        <v>71</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" hidden="1">
+      <c r="A76" s="5">
+        <v>72</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" hidden="1">
+      <c r="A77" s="5">
+        <v>73</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" hidden="1">
+      <c r="A78" s="5">
+        <v>74</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" hidden="1">
+      <c r="A79" s="5">
+        <v>75</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" hidden="1">
+      <c r="A80" s="5">
+        <v>76</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" hidden="1">
+      <c r="A81" s="5">
+        <v>77</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1">
+      <c r="A82" s="5">
+        <v>78</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1">
+      <c r="A83" s="5">
+        <v>79</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1">
+      <c r="A84" s="5">
+        <v>80</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1">
+      <c r="A85" s="5">
+        <v>81</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1">
+      <c r="A86" s="5">
+        <v>82</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1">
+      <c r="A87" s="5">
+        <v>83</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1">
+      <c r="A88" s="5">
+        <v>84</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1">
+      <c r="A89" s="5">
+        <v>85</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1">
+      <c r="A90" s="5">
+        <v>86</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1">
+      <c r="A91" s="5">
+        <v>87</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1">
+      <c r="A92" s="5">
+        <v>88</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1">
+      <c r="A93" s="5">
+        <v>89</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1">
+      <c r="A94" s="5">
+        <v>90</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="5">
+        <v>91</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1">
+      <c r="A96" s="5">
+        <v>92</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1">
+      <c r="A97" s="5">
+        <v>93</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1">
+      <c r="A98" s="5">
+        <v>94</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="5">
+        <v>95</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1">
+      <c r="A100" s="5">
+        <v>96</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1">
+      <c r="A101" s="5">
+        <v>97</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1">
+      <c r="A102" s="5">
+        <v>98</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G102" xr:uid="{9D914D93-2EF7-46FD-952F-9181B9DA8F64}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="外製"/>
+        <filter val="不明"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{0141F275-8B25-4383-9E70-45488E0DC30E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>